--- a/Dados_westernblot_form_HTR8.xlsx
+++ b/Dados_westernblot_form_HTR8.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="13">
   <si>
     <t xml:space="preserve">Endoglina</t>
   </si>
@@ -50,7 +50,16 @@
     <t xml:space="preserve">prot</t>
   </si>
   <si>
+    <t xml:space="preserve">tipo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Endoglin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replicate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean</t>
   </si>
 </sst>
 </file>
@@ -60,7 +69,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,6 +97,12 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -132,7 +147,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -146,6 +161,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,7 +498,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -492,272 +511,466 @@
       <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>0.440473</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>0.991034</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>1.568493</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>1</v>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
-        <v>0.702168</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
+        <f aca="false">AVERAGE(A2:A4)</f>
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
-        <v>0.909697</v>
+        <v>0.702168</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
-        <v>1.38624</v>
+        <v>0.909697</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
-        <v>0.626049</v>
+        <v>1.38624</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
-        <v>0.760704</v>
+        <f aca="false">AVERAGE(A6:A8)</f>
+        <v>0.999368333333333</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
-        <v>1.278118</v>
+        <v>0.626049</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
-        <v>0.382994</v>
+        <v>0.760704</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
-        <v>0.662787</v>
+        <v>1.278118</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
-        <v>0.862051</v>
+        <f aca="false">AVERAGE(A10:A12)</f>
+        <v>0.888290333333333</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
-        <v>0.338835</v>
+        <v>0.382994</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
-        <v>0.326802</v>
+        <v>0.662787</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
-        <v>2.334363</v>
+        <v>0.862051</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
-        <v>0.320602</v>
+        <f aca="false">AVERAGE(A14:A16)</f>
+        <v>0.635944</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
-        <v>2.430566</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>2</v>
+        <v>0.338835</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
-        <v>1.98595</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>2</v>
+        <v>0.326802</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
-        <v>0.466186</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
+        <v>2.334363</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
-        <v>2.536274</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
+        <f aca="false">AVERAGE(A18:A20)</f>
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
-        <v>2.040811</v>
+        <v>0.320602</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
-        <v>2.182363</v>
+        <v>2.430566</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
-        <v>1.618182</v>
+        <v>1.98595</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
+        <f aca="false">AVERAGE(A22:A24)</f>
+        <v>1.57903933333333</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
+        <v>0.466186</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
+        <v>2.536274</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
+        <v>2.040811</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="n">
+        <f aca="false">AVERAGE(A26:A28)</f>
+        <v>1.68109033333333</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="n">
+        <v>2.182363</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="n">
+        <v>1.618182</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="n">
         <v>1.244529</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <f aca="false">AVERAGE(A30:A32)</f>
+        <v>1.68169133333333</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
